--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487891_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487891_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9871</v>
+        <v>7.2376</v>
       </c>
       <c r="E2" t="n">
-        <v>6.2518</v>
+        <v>7.561</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2647</v>
+        <v>-0.3234</v>
       </c>
       <c r="G2" t="n">
         <v>2.8465</v>
@@ -610,13 +610,13 @@
         <v>1.8731</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.4431</v>
+        <v>-0.1926</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.2025</v>
+        <v>0.1067</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2407</v>
+        <v>-0.2994</v>
       </c>
       <c r="V2" t="n">
         <v>2.9188</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.1513</v>
+        <v>5.1992</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1223</v>
+        <v>5.7885</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.971</v>
+        <v>-0.5893</v>
       </c>
       <c r="G3" t="n">
         <v>5.3722</v>
@@ -688,13 +688,13 @@
         <v>1.4568</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0752</v>
+        <v>-0.0273</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0339</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.1091</v>
+        <v>-0.7274</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3538</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4705</v>
+        <v>2.3397</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2083</v>
+        <v>2.6958</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.7378</v>
+        <v>-0.3561</v>
       </c>
       <c r="G4" t="n">
         <v>3.4852</v>
@@ -766,13 +766,13 @@
         <v>1.8731</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0026</v>
+        <v>-0.1282</v>
       </c>
       <c r="T4" t="n">
-        <v>1.1892</v>
+        <v>0.6768</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.1867</v>
+        <v>-0.805</v>
       </c>
       <c r="V4" t="n">
         <v>-1.6416</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. ROMERO SANCHEZ</t>
+          <t>N. OKEKE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5233</v>
+        <v>1.6819</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3975</v>
+        <v>1.7571</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1258</v>
+        <v>-0.0752</v>
       </c>
       <c r="G5" t="n">
-        <v>1.503</v>
+        <v>1.0454</v>
       </c>
       <c r="H5" t="n">
-        <v>0.369</v>
+        <v>0.8723</v>
       </c>
       <c r="I5" t="n">
-        <v>1.134</v>
+        <v>0.1731</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9194</v>
+        <v>1.4701</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0384</v>
+        <v>0.9786</v>
       </c>
       <c r="L5" t="n">
-        <v>1.881</v>
+        <v>0.4915</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4164</v>
+        <v>-0.4247</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3306</v>
+        <v>-0.1063</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.747</v>
+        <v>-0.3184</v>
       </c>
       <c r="P5" t="n">
         <v>0.6244</v>
@@ -844,28 +844,28 @@
         <v>0.6244</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2538</v>
+        <v>-0.2213</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5219</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2682</v>
+        <v>0.3054</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3503</v>
+        <v>0.2335</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.8137</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3503</v>
+        <v>-0.5802</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. OKEKE</t>
+          <t>S. ROMERO SANCHEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,40 +877,40 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0897</v>
+        <v>1.6179</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3704</v>
+        <v>1.4627</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2807</v>
+        <v>0.1552</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0454</v>
+        <v>1.503</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8723</v>
+        <v>0.369</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1731</v>
+        <v>1.134</v>
       </c>
       <c r="J6" t="n">
-        <v>1.4701</v>
+        <v>1.9194</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9786</v>
+        <v>0.0384</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4915</v>
+        <v>1.881</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4247</v>
+        <v>-0.4164</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1063</v>
+        <v>0.3306</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3184</v>
+        <v>-0.747</v>
       </c>
       <c r="P6" t="n">
         <v>0.6244</v>
@@ -922,22 +922,22 @@
         <v>0.6244</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8136</v>
+        <v>-0.1592</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9134</v>
+        <v>-0.4567</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0998</v>
+        <v>0.2975</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2335</v>
+        <v>-0.3503</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8137</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5802</v>
+        <v>-0.3503</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4777</v>
+        <v>-0.8694</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3942</v>
+        <v>2.8399</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.9166</v>
+        <v>-3.7093</v>
       </c>
       <c r="G7" t="n">
         <v>-3.0727</v>
@@ -1000,13 +1000,13 @@
         <v>1.4568</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8824</v>
+        <v>1.5353</v>
       </c>
       <c r="T7" t="n">
-        <v>1.2669</v>
+        <v>0.7125</v>
       </c>
       <c r="U7" t="n">
-        <v>1.6155</v>
+        <v>0.8228</v>
       </c>
       <c r="V7" t="n">
         <v>0.4599</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.358</v>
+        <v>-1.3683</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5612</v>
+        <v>-1.4541</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2032</v>
+        <v>0.0858</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2557</v>
@@ -1078,13 +1078,13 @@
         <v>0.2081</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0398</v>
+        <v>0.0295</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4567</v>
+        <v>-0.3495</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4965</v>
+        <v>0.3791</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3503</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. TREVIÑO QUINTILLÁ</t>
+          <t>R. BLAK MOLLER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2992</v>
+        <v>-2.6308</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2668</v>
+        <v>-2.876</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.5661</v>
+        <v>0.2452</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.8239</v>
+        <v>-2.3812</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1727</v>
+        <v>-1.533</v>
       </c>
       <c r="I9" t="n">
-        <v>-4.6512</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.8968</v>
+        <v>-2.6832</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3705</v>
+        <v>-1.3328</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.2673</v>
+        <v>-1.3504</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.927</v>
+        <v>0.3019</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5432</v>
+        <v>-0.2002</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3838</v>
+        <v>0.5021</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2081</v>
+        <v>0.8325</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2893</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0812</v>
+        <v>0.8325</v>
       </c>
       <c r="S9" t="n">
-        <v>2.149</v>
+        <v>-0.6221</v>
       </c>
       <c r="T9" t="n">
-        <v>2.3042</v>
+        <v>-0.1928</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1552</v>
+        <v>-0.4292</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5838</v>
+        <v>-0.4599</v>
       </c>
       <c r="W9" t="n">
-        <v>3.1488</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.565</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. BLAK MOLLER</t>
+          <t>J. CERA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4205</v>
+        <v>-3.6401</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.519</v>
+        <v>-2.0521</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0984</v>
+        <v>-1.588</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.3812</v>
+        <v>-2.7193</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.533</v>
+        <v>-1.4775</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8483000000000001</v>
+        <v>-1.2418</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.6832</v>
+        <v>-2.2211</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.3328</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3504</v>
+        <v>-1.5643</v>
       </c>
       <c r="M10" t="n">
-        <v>0.3019</v>
+        <v>-0.4982</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2002</v>
+        <v>-0.8207</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5021</v>
+        <v>0.3225</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8325</v>
+        <v>0.4162</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8325</v>
+        <v>0.4162</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4118</v>
+        <v>-0.403</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8358</v>
+        <v>-0.4148</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.576</v>
+        <v>0.0118</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.4599</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.4599</v>
+        <v>-1.5178</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. CERA RODRIGUEZ</t>
+          <t>P. TREVIÑO QUINTILLÁ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8419</v>
+        <v>-3.8092</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.2245</v>
+        <v>-1.0376</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6173</v>
+        <v>-2.7716</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.7193</v>
+        <v>-4.8239</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4775</v>
+        <v>-0.1727</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2418</v>
+        <v>-4.6512</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.2211</v>
+        <v>-2.8968</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6568000000000001</v>
+        <v>0.3705</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.5643</v>
+        <v>-3.2673</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4982</v>
+        <v>-1.927</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8207</v>
+        <v>-0.5432</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3225</v>
+        <v>-1.3838</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4162</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.2893</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4162</v>
+        <v>2.0812</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6048</v>
+        <v>0.639</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5872000000000001</v>
+        <v>0.9997</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0176</v>
+        <v>-0.3607</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9340000000000001</v>
+        <v>0.5838</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5838</v>
+        <v>3.1488</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.5178</v>
+        <v>-2.565</v>
       </c>
     </row>
     <row r="12">
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.78</v>
+        <v>5.7585</v>
       </c>
       <c r="E12" t="n">
-        <v>13.7066</v>
+        <v>14.6852</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.9268</v>
+        <v>-8.9267</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.0004999999999988347</v>
+        <v>-0.0005000000000006111</v>
       </c>
       <c r="H12" t="n">
         <v>-4.797</v>
@@ -1363,10 +1363,10 @@
         <v>4.7963</v>
       </c>
       <c r="J12" t="n">
-        <v>9.431000000000001</v>
+        <v>9.430999999999997</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1413000000000002</v>
+        <v>-0.1413000000000003</v>
       </c>
       <c r="L12" t="n">
         <v>9.572299999999998</v>
@@ -1390,16 +1390,16 @@
         <v>11.4466</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5284999999999997</v>
+        <v>0.4501000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2766999999999997</v>
+        <v>1.2553</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8052999999999999</v>
+        <v>-0.8051000000000004</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1061</v>
+        <v>0.1060999999999999</v>
       </c>
       <c r="W12" t="n">
         <v>10.2423</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.3814</v>
+        <v>4.787</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3498</v>
+        <v>3.6713</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0316</v>
+        <v>1.1157</v>
       </c>
       <c r="G13" t="n">
         <v>2.7523</v>
@@ -1468,13 +1468,13 @@
         <v>0.2081</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3275</v>
+        <v>0.7332</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3543</v>
+        <v>-0.0328</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6818</v>
+        <v>0.766</v>
       </c>
       <c r="V13" t="n">
         <v>2.3421</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.3656</v>
+        <v>1.8068</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4272</v>
+        <v>2.7842</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0616</v>
+        <v>-0.9774</v>
       </c>
       <c r="G14" t="n">
         <v>3.2495</v>
@@ -1546,13 +1546,13 @@
         <v>0.6244</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3648</v>
+        <v>0.806</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4626</v>
+        <v>0.8197</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0978</v>
+        <v>-0.0136</v>
       </c>
       <c r="V14" t="n">
         <v>-0.5838</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>G. MCKAY JR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3877</v>
+        <v>1.0591</v>
       </c>
       <c r="E15" t="n">
-        <v>3.2747</v>
+        <v>0.3754</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.887</v>
+        <v>0.6838</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.599</v>
+        <v>0.2515</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.9685</v>
+        <v>-0.5502</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.6305</v>
+        <v>0.8017</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.5577</v>
+        <v>0.5944</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.9519</v>
+        <v>-0.738</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6058</v>
+        <v>1.3324</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.0413</v>
+        <v>-0.3429</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0166</v>
+        <v>0.1877</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.0247</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.2081</v>
+        <v>0.4162</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.2487</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.0406</v>
+        <v>0.4162</v>
       </c>
       <c r="S15" t="n">
-        <v>3.6841</v>
+        <v>-0.1994</v>
       </c>
       <c r="T15" t="n">
-        <v>3.41</v>
+        <v>-0.2191</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2741</v>
+        <v>0.0196</v>
       </c>
       <c r="V15" t="n">
-        <v>1.5107</v>
+        <v>0.5908</v>
       </c>
       <c r="W15" t="n">
-        <v>2.6711</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1604</v>
+        <v>0.5908</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. MCKAY JR</t>
+          <t>R. LLAMAS MARTINEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8385</v>
+        <v>0.8013</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2682</v>
+        <v>0.2762</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5703</v>
+        <v>0.5251</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2515</v>
+        <v>-1.9374</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.5502</v>
+        <v>0.8956</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8017</v>
+        <v>-2.833</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5944</v>
+        <v>-1.1413</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.738</v>
+        <v>0.0915</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3324</v>
+        <v>-1.2328</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3429</v>
+        <v>-0.7961</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1877</v>
+        <v>0.8041</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-1.6002</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4162</v>
+        <v>0.6244</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4201</v>
+        <v>0.7169</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3262</v>
+        <v>0.02</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0939</v>
+        <v>0.6968</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5908</v>
+        <v>1.3975</v>
       </c>
       <c r="W16" t="n">
+        <v>1.3975</v>
+      </c>
+      <c r="X16" t="n">
         <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0.5908</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. LLAMAS MARTINEZ</t>
+          <t>M. DENG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4838</v>
+        <v>0.031</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0452</v>
+        <v>3.4177</v>
       </c>
       <c r="F17" t="n">
-        <v>0.529</v>
+        <v>-3.3866</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.9374</v>
+        <v>2.4631</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8956</v>
+        <v>0.8466</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.833</v>
+        <v>1.6165</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.1413</v>
+        <v>3.5001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0915</v>
+        <v>0.9978</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2328</v>
+        <v>2.5023</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7961</v>
+        <v>-1.037</v>
       </c>
       <c r="N17" t="n">
-        <v>0.8041</v>
+        <v>-0.1512</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.6002</v>
+        <v>-0.8858</v>
       </c>
       <c r="P17" t="n">
         <v>0.6244</v>
@@ -1780,22 +1780,22 @@
         <v>0.6244</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3993</v>
+        <v>-0.7214</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3014</v>
+        <v>-0.3124</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7007</v>
+        <v>-0.409</v>
       </c>
       <c r="V17" t="n">
-        <v>1.3975</v>
+        <v>-2.3351</v>
       </c>
       <c r="W17" t="n">
-        <v>1.3975</v>
+        <v>0.23</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-2.565</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.445</v>
+        <v>-0.103</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1798</v>
+        <v>1.287</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6248</v>
+        <v>-1.39</v>
       </c>
       <c r="G18" t="n">
         <v>0.5789</v>
@@ -1858,13 +1858,13 @@
         <v>0.2081</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0021</v>
+        <v>-0.6601</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6524</v>
+        <v>-0.5453</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3497</v>
+        <v>-0.1148</v>
       </c>
       <c r="V18" t="n">
         <v>-0.23</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. DENG</t>
+          <t>D. CEBOLLA PORCAR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8531</v>
+        <v>-0.1465</v>
       </c>
       <c r="E19" t="n">
-        <v>2.8819</v>
+        <v>-0.8603</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.735</v>
+        <v>0.7138</v>
       </c>
       <c r="G19" t="n">
-        <v>2.4631</v>
+        <v>1.4876</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8466</v>
+        <v>1.9766</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6165</v>
+        <v>-0.489</v>
       </c>
       <c r="J19" t="n">
-        <v>3.5001</v>
+        <v>2.1205</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9978</v>
+        <v>1.5115</v>
       </c>
       <c r="L19" t="n">
-        <v>2.5023</v>
+        <v>0.609</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.037</v>
+        <v>-0.6329</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1512</v>
+        <v>0.4652</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8858</v>
+        <v>-1.0981</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6244</v>
+        <v>-2.2893</v>
       </c>
       <c r="Q19" t="n">
+        <v>-3.3299</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.0406</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.4228</v>
+      </c>
+      <c r="V19" t="n">
+        <v>-0.1168</v>
+      </c>
+      <c r="W19" t="n">
         <v>0</v>
       </c>
-      <c r="R19" t="n">
-        <v>0.6244</v>
-      </c>
-      <c r="S19" t="n">
-        <v>-1.6056</v>
-      </c>
-      <c r="T19" t="n">
-        <v>-0.8482</v>
-      </c>
-      <c r="U19" t="n">
-        <v>-0.7574</v>
-      </c>
-      <c r="V19" t="n">
-        <v>-2.3351</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0.23</v>
-      </c>
       <c r="X19" t="n">
-        <v>-2.565</v>
+        <v>-0.1168</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. CEBOLLA PORCAR</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.422</v>
+        <v>-0.4149</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8247</v>
+        <v>1.1316</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4026</v>
+        <v>-1.5465</v>
       </c>
       <c r="G20" t="n">
-        <v>1.4876</v>
+        <v>-3.599</v>
       </c>
       <c r="H20" t="n">
-        <v>1.9766</v>
+        <v>-0.9685</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.489</v>
+        <v>-2.6305</v>
       </c>
       <c r="J20" t="n">
-        <v>2.1205</v>
+        <v>-1.5577</v>
       </c>
       <c r="K20" t="n">
-        <v>1.5115</v>
+        <v>-0.9519</v>
       </c>
       <c r="L20" t="n">
-        <v>0.609</v>
+        <v>-0.6058</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6329</v>
+        <v>-2.0413</v>
       </c>
       <c r="N20" t="n">
-        <v>0.4652</v>
+        <v>-0.0166</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0981</v>
+        <v>-2.0247</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.2893</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.3299</v>
+        <v>-1.2487</v>
       </c>
       <c r="R20" t="n">
         <v>1.0406</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5036</v>
+        <v>1.8815</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6153</v>
+        <v>1.2669</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1117</v>
+        <v>0.6146</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1168</v>
+        <v>1.5107</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.6711</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1168</v>
+        <v>-1.1604</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. ORENGA IMAZ</t>
+          <t>J. LLAMAS PRADO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4837</v>
+        <v>-3.0706</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4704</v>
+        <v>-0.2175</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.0133</v>
+        <v>-2.8531</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1575</v>
+        <v>-4.583</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.2068</v>
+        <v>-0.5352</v>
       </c>
       <c r="I21" t="n">
-        <v>1.3642</v>
+        <v>-4.0478</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5976</v>
+        <v>-2.1295</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.676</v>
+        <v>-0.1431</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0784</v>
+        <v>-1.9864</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7551</v>
+        <v>-2.4535</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5308</v>
+        <v>-0.3921</v>
       </c>
       <c r="O21" t="n">
-        <v>1.2859</v>
+        <v>-2.0614</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.2081</v>
+        <v>-1.0406</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2081</v>
+        <v>1.0406</v>
       </c>
       <c r="S21" t="n">
-        <v>0.09130000000000001</v>
+        <v>-0.7059</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3353</v>
+        <v>-0.55</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.244</v>
+        <v>-0.1559</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.7325</v>
+        <v>2.2183</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.5026</v>
       </c>
       <c r="X21" t="n">
-        <v>-3.7325</v>
+        <v>-1.2843</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. AMADASUN</t>
+          <t>P. ORENGA IMAZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9582</v>
+        <v>-3.3996</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4686</v>
+        <v>-0.4704</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4897</v>
+        <v>-2.9291</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8204</v>
+        <v>0.1575</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0065</v>
+        <v>-1.2068</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.8139999999999999</v>
+        <v>1.3642</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0612</v>
+        <v>-0.5976</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.1004</v>
+        <v>-0.676</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0392</v>
+        <v>0.0784</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7593</v>
+        <v>0.7551</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0939</v>
+        <v>-0.5308</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8532</v>
+        <v>1.2859</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.8731</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.0812</v>
+        <v>-0.2081</v>
       </c>
       <c r="R22" t="n">
         <v>0.2081</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.09719999999999999</v>
+        <v>0.1755</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3262</v>
+        <v>0.3353</v>
       </c>
       <c r="U22" t="n">
-        <v>0.229</v>
+        <v>-0.1598</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.1675</v>
+        <v>-3.7325</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.1675</v>
+        <v>-3.7325</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. LLAMAS PRADO</t>
+          <t>M. AMADASUN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0747</v>
+        <v>-3.9876</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6462</v>
+        <v>-2.4686</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.4285</v>
+        <v>-1.519</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.583</v>
+        <v>-0.8204</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5352</v>
+        <v>-0.0065</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.0478</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.1295</v>
+        <v>-0.0612</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.1431</v>
+        <v>-0.1004</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.9864</v>
+        <v>0.0392</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.4535</v>
+        <v>-0.7593</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3921</v>
+        <v>0.0939</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.0614</v>
+        <v>-0.8532</v>
       </c>
       <c r="P23" t="n">
+        <v>-1.8731</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-2.0812</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.2081</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.1266</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.3262</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.1997</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-1.1675</v>
+      </c>
+      <c r="W23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>-1.0406</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.0406</v>
-      </c>
-      <c r="S23" t="n">
-        <v>-1.71</v>
-      </c>
-      <c r="T23" t="n">
-        <v>-0.9786</v>
-      </c>
-      <c r="U23" t="n">
-        <v>-0.7313</v>
-      </c>
-      <c r="V23" t="n">
-        <v>2.2183</v>
-      </c>
-      <c r="W23" t="n">
-        <v>3.5026</v>
-      </c>
       <c r="X23" t="n">
-        <v>-1.2843</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="24">
@@ -2281,40 +2281,40 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.7797</v>
+        <v>-2.637</v>
       </c>
       <c r="E24" t="n">
-        <v>8.926500000000001</v>
+        <v>8.926600000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-13.7064</v>
+        <v>-11.5633</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0005999999999986017</v>
+        <v>0.0005999999999990457</v>
       </c>
       <c r="H24" t="n">
-        <v>4.796900000000001</v>
+        <v>4.7969</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.796500000000001</v>
+        <v>-4.7965</v>
       </c>
       <c r="J24" t="n">
         <v>9.431699999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>4.655600000000002</v>
+        <v>4.655600000000001</v>
       </c>
       <c r="L24" t="n">
         <v>4.775900000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-9.431100000000001</v>
+        <v>-9.431099999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1413</v>
+        <v>0.1412999999999998</v>
       </c>
       <c r="O24" t="n">
-        <v>-9.5724</v>
+        <v>-9.572399999999998</v>
       </c>
       <c r="P24" t="n">
         <v>-5.2029</v>
@@ -2326,13 +2326,13 @@
         <v>6.243599999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5284</v>
+        <v>2.671700000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8053</v>
+        <v>0.8051999999999997</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2767999999999999</v>
+        <v>1.8664</v>
       </c>
       <c r="V24" t="n">
         <v>-0.1063000000000005</v>
